--- a/www/download/IND.labour_force_value.s.mv.rpA2.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14628.042</t>
+          <t>14628042190.8374</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15544.953</t>
+          <t>15544953277.4964</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15109.327</t>
+          <t>15109327132.9598</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15733.039</t>
+          <t>15733039147.8668</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>17247.597</t>
+          <t>17247597456.6853</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>17261.02</t>
+          <t>17261019567.6964</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17113.161</t>
+          <t>17113161256.2392</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18580.573</t>
+          <t>18580573479.4112</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>20281.252</t>
+          <t>20281251802.9316</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>23861.054</t>
+          <t>23861054278.7051</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>25886.563</t>
+          <t>25886563409.2138</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>26047.079</t>
+          <t>26047079449.149</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>27403.05</t>
+          <t>27403049959.8549</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>27492.857</t>
+          <t>27492857234.8309</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>28077.69</t>
+          <t>28077689901.8906</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9539.267</t>
+          <t>9539266740.56721</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9381.278</t>
+          <t>9381278242.21465</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8254.867</t>
+          <t>8254866646.09913</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8546.862</t>
+          <t>8546862309.15576</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8795.547</t>
+          <t>8795547032.47408</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8614.417</t>
+          <t>8614417071.88503</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8871.627</t>
+          <t>8871626774.43957</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9036.301</t>
+          <t>9036301223.36502</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9830.437</t>
+          <t>9830437167.17755</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>10445.767</t>
+          <t>10445766565.6381</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10527.893</t>
+          <t>10527893461.1966</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10746.116</t>
+          <t>10746116489.1945</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>10903.16</t>
+          <t>10903159517.8783</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>10773.032</t>
+          <t>10773031788.1404</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9986.888</t>
+          <t>9986888190.23327</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11023.737</t>
+          <t>11023736976.3116</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11375.771</t>
+          <t>11375771192.1043</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10945.338</t>
+          <t>10945338077.0258</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11223.996</t>
+          <t>11223996090.7726</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>12536.142</t>
+          <t>12536141914.4075</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13446.884</t>
+          <t>13446883813.5677</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14625.027</t>
+          <t>14625027038.5231</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15977.365</t>
+          <t>15977365195.8524</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>19530.036</t>
+          <t>19530036472.1357</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>20891.766</t>
+          <t>20891766414.335</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>20799.357</t>
+          <t>20799357063.6683</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>20797.974</t>
+          <t>20797973738.592</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>20308.887</t>
+          <t>20308887126.2903</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>18972.37</t>
+          <t>18972370178.7166</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>19903.212</t>
+          <t>19903212189.1483</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1858.711</t>
+          <t>1858710678.19823</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1728.411</t>
+          <t>1728411113.5115</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1414.112</t>
+          <t>1414111937.31163</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1679.33</t>
+          <t>1679329666.86469</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1539.82</t>
+          <t>1539820028.90789</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1341.448</t>
+          <t>1341448242.76359</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1354.837</t>
+          <t>1354837264.0492</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1347.242</t>
+          <t>1347241846.72433</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1424.571</t>
+          <t>1424571021.90264</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1482.755</t>
+          <t>1482755470.94987</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1465.869</t>
+          <t>1465869208.08279</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1524.578</t>
+          <t>1524577607.85564</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1734.483</t>
+          <t>1734483323.83507</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1996.715</t>
+          <t>1996714890.66632</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2210.529</t>
+          <t>2210529101.68755</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>64123.45</t>
+          <t>64123450355.9119</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>64133.688</t>
+          <t>64133688103.0367</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62588.348</t>
+          <t>62588347779.2225</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>63628.024</t>
+          <t>63628023555.9015</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60667.84</t>
+          <t>60667839802.7095</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>63080.441</t>
+          <t>63080440524.805</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>62838.112</t>
+          <t>62838111748.2016</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>63422.491</t>
+          <t>63422490827.4221</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>64451.72</t>
+          <t>64451719637.9391</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>69547.971</t>
+          <t>69547971261.0647</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>74258.638</t>
+          <t>74258638015.0628</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>79299.165</t>
+          <t>79299164548.4806</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>83678.446</t>
+          <t>83678446395.1372</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>90351.677</t>
+          <t>90351677460.5981</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>91228.932</t>
+          <t>91228932186.1507</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24263.777</t>
+          <t>24263777152.7062</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>24042.336</t>
+          <t>24042335986.5696</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>23160.924</t>
+          <t>23160923811.9918</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>24935.932</t>
+          <t>24935931988.715</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>26834.743</t>
+          <t>26834742951.2363</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30090.51</t>
+          <t>30090509636.3343</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>32387.618</t>
+          <t>32387618340.1924</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32919.318</t>
+          <t>32919317976.772</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>35544.032</t>
+          <t>35544032340.1917</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>38054.234</t>
+          <t>38054234429.9735</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>41101.219</t>
+          <t>41101219492.055</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>43299.071</t>
+          <t>43299070774.7804</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>42795.383</t>
+          <t>42795383140.6557</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>43580.868</t>
+          <t>43580868041.7033</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>39495.798</t>
+          <t>39495798182.8928</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>726254.061</t>
+          <t>726254061345.253</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>724157.933</t>
+          <t>724157932838.686</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>732103.222</t>
+          <t>732103221512.297</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>724139.234</t>
+          <t>724139233882.677</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>709685.367</t>
+          <t>709685367081.163</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>693238.677</t>
+          <t>693238677092.401</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>695110.752</t>
+          <t>695110751712.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>700203.802</t>
+          <t>700203802128.135</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>696850.128</t>
+          <t>696850127687.084</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>696356.291</t>
+          <t>696356290580.631</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>693916.722</t>
+          <t>693916722010.507</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>696755.478</t>
+          <t>696755477649.985</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>653840.436</t>
+          <t>653840435886.276</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>693102.488</t>
+          <t>693102488131.407</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>701507.018</t>
+          <t>701507018200.627</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>448.494</t>
+          <t>448494259.518721</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>456.846</t>
+          <t>456845852.156961</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>402.791</t>
+          <t>402791043.046987</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>426.13</t>
+          <t>426130238.178358</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>470.923</t>
+          <t>470922600.730267</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>478.188</t>
+          <t>478187855.228422</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>530.056</t>
+          <t>530055884.405081</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>566.098</t>
+          <t>566097598.660818</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>652.77</t>
+          <t>652769644.387176</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>644.018</t>
+          <t>644017511.065644</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>646.391</t>
+          <t>646390538.341227</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>662.21</t>
+          <t>662209877.899817</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>643.209</t>
+          <t>643209465.609126</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>770.118</t>
+          <t>770117687.756549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>650.998</t>
+          <t>650997873.721466</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4228.974</t>
+          <t>4228973512.95144</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>6002.694</t>
+          <t>6002693680.78197</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>5581.723</t>
+          <t>5581723204.85016</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5548.966</t>
+          <t>5548966238.94919</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5393.16</t>
+          <t>5393159965.37371</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5229.455</t>
+          <t>5229455154.60107</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5408.55</t>
+          <t>5408550016.88198</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5571.874</t>
+          <t>5571873585.46359</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5916.696</t>
+          <t>5916695962.71644</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6397.595</t>
+          <t>6397594536.82042</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6830.253</t>
+          <t>6830253483.03546</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6761.568</t>
+          <t>6761568303.0104</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>7017.396</t>
+          <t>7017395546.24956</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>7046.288</t>
+          <t>7046287600.56634</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>6204.904</t>
+          <t>6204904428.73561</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>110748.976</t>
+          <t>110748975647.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>100594.602</t>
+          <t>100594602484.196</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>88321.151</t>
+          <t>88321151466.2556</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93114.403</t>
+          <t>93114403085.2604</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>96756.279</t>
+          <t>96756279269.6339</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>101299.831</t>
+          <t>101299830660.1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>99647.304</t>
+          <t>99647304015.2165</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>100373.514</t>
+          <t>100373513848.545</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>113191.635</t>
+          <t>113191634584.611</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>115575.898</t>
+          <t>115575898389.784</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>109369.408</t>
+          <t>109369407941.3</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>110046.093</t>
+          <t>110046093039.782</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>114022.098</t>
+          <t>114022097563.148</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>110874.69</t>
+          <t>110874689927.222</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>105582.481</t>
+          <t>105582480743.811</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8143.057</t>
+          <t>8143056898.80057</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>8119.424</t>
+          <t>8119423954.48557</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6799.067</t>
+          <t>6799066571.39832</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7452.301</t>
+          <t>7452301208.02992</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7670.37</t>
+          <t>7670369846.80436</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7480.933</t>
+          <t>7480932587.41995</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7985.505</t>
+          <t>7985504996.31648</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>8364.974</t>
+          <t>8364973619.61368</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>9480.489</t>
+          <t>9480488734.07139</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9612.875</t>
+          <t>9612874529.08307</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9716.907</t>
+          <t>9716907335.05728</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10022.078</t>
+          <t>10022078066.0314</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10203.759</t>
+          <t>10203759236.8242</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>9978.218</t>
+          <t>9978218248.39839</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>8803.118</t>
+          <t>8803117855.62635</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22762.733</t>
+          <t>22762732833.2579</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22946.181</t>
+          <t>22946181122.9788</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20761.635</t>
+          <t>20761635229.1557</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23958.081</t>
+          <t>23958080947.0004</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>26927.044</t>
+          <t>26927044269.2789</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>28645.735</t>
+          <t>28645734973.029</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31332.3</t>
+          <t>31332300352.9247</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>34023.45</t>
+          <t>34023449577.8423</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>38635.992</t>
+          <t>38635992086.4918</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>41537.518</t>
+          <t>41537518059.6482</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>43609.377</t>
+          <t>43609377368.125</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>46250.916</t>
+          <t>46250915501.31</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>47309.053</t>
+          <t>47309052736.2313</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47162.423</t>
+          <t>47162422953.6292</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>40772.761</t>
+          <t>40772760932.476</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>750.359</t>
+          <t>750358928.752933</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>758.49</t>
+          <t>758490475.393204</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>756.157</t>
+          <t>756156502.207288</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>764.878</t>
+          <t>764877907.471566</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>728.213</t>
+          <t>728213110.873988</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>807.596</t>
+          <t>807595889.559732</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>817.771</t>
+          <t>817770540.062235</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1024.959</t>
+          <t>1024958880.35365</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1193.795</t>
+          <t>1193795099.733</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1245.398</t>
+          <t>1245398091.95202</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1214.78</t>
+          <t>1214780477.15044</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1251.517</t>
+          <t>1251516636.10941</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1296.301</t>
+          <t>1296301426.59062</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1427.095</t>
+          <t>1427094983.11206</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1202.077</t>
+          <t>1202077133.16544</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4871.294</t>
+          <t>4871294228.45891</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5017.084</t>
+          <t>5017083648.53174</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4433.578</t>
+          <t>4433578303.79877</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4837.308</t>
+          <t>4837307611.50714</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5052.89</t>
+          <t>5052889882.32258</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4749.061</t>
+          <t>4749061042.37642</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4983.785</t>
+          <t>4983784564.99126</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5111.591</t>
+          <t>5111590589.37856</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>5661.499</t>
+          <t>5661499210.51683</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5982.329</t>
+          <t>5982328629.25398</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6173.247</t>
+          <t>6173247458.74297</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>6403.06</t>
+          <t>6403060441.45419</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6539.876</t>
+          <t>6539875714.21513</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6582.072</t>
+          <t>6582072419.8741</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6048.901</t>
+          <t>6048901469.81657</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>49867.112</t>
+          <t>49867111913.7753</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52206.11</t>
+          <t>52206110199.0707</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45956.743</t>
+          <t>45956743367.1736</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51566.988</t>
+          <t>51566988260.562</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>56977.482</t>
+          <t>56977482441.4182</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>58033.933</t>
+          <t>58033933108.9813</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>62484.244</t>
+          <t>62484244370.4402</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>65380.162</t>
+          <t>65380162164.4904</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>71428.469</t>
+          <t>71428469141.8758</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>74755.387</t>
+          <t>74755387010.1027</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>75595.243</t>
+          <t>75595243108.0172</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>74368.192</t>
+          <t>74368192462.386</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>75547.75</t>
+          <t>75547749619.8031</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>74779.796</t>
+          <t>74779795823.2077</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>69586.618</t>
+          <t>69586617769.9632</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>48989.347</t>
+          <t>48989347473.4448</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50566.441</t>
+          <t>50566440931.8471</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>49011.383</t>
+          <t>49011383364.6447</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>54399.366</t>
+          <t>54399366149.1929</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>58710.843</t>
+          <t>58710842880.717</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>62467.837</t>
+          <t>62467836863.2693</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>66479.21</t>
+          <t>66479210058.7923</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>69383.974</t>
+          <t>69383974189.3082</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>73894.938</t>
+          <t>73894937894.7099</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>78706.577</t>
+          <t>78706577380.5966</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>79571.928</t>
+          <t>79571927685.8171</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>80831.096</t>
+          <t>80831095617.6441</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>80186.328</t>
+          <t>80186328260.1844</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>72055.266</t>
+          <t>72055265501.6513</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>66099.713</t>
+          <t>66099713237.5569</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3930.569</t>
+          <t>3930568623.60658</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4098.25</t>
+          <t>4098249599.62392</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3949.414</t>
+          <t>3949413935.02797</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4181.535</t>
+          <t>4181535131.68983</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4522.223</t>
+          <t>4522222709.20582</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4837.114</t>
+          <t>4837113580.35815</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4736.352</t>
+          <t>4736351697.49119</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5642.803</t>
+          <t>5642803097.27902</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5934.338</t>
+          <t>5934338382.54562</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>6353.505</t>
+          <t>6353504619.59274</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>6257.132</t>
+          <t>6257132398.59612</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>6865.653</t>
+          <t>6865652560.26134</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>7356.721</t>
+          <t>7356720553.66807</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>7606.313</t>
+          <t>7606312703.98</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7369.683</t>
+          <t>7369683053.28537</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5987.048</t>
+          <t>5987047860.11518</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5611.765</t>
+          <t>5611764906.62243</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5328.277</t>
+          <t>5328277132.83497</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5338.701</t>
+          <t>5338701266.72392</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5726.46</t>
+          <t>5726460399.99731</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5583.337</t>
+          <t>5583337201.44744</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5488.331</t>
+          <t>5488330510.01085</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5981.881</t>
+          <t>5981880714.28856</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6477.064</t>
+          <t>6477064283.88827</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5803.136</t>
+          <t>5803135616.27845</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5828.144</t>
+          <t>5828143572.09295</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5628.065</t>
+          <t>5628064997.93108</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5839.06</t>
+          <t>5839060146.62961</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5415.023</t>
+          <t>5415023026.65369</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5031.859</t>
+          <t>5031859077.45512</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>34660.188</t>
+          <t>34660187525.014</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>35844.662</t>
+          <t>35844661639.856</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>33355.83</t>
+          <t>33355830337.4129</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31193.455</t>
+          <t>31193455040.1764</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>34559.977</t>
+          <t>34559976617.3472</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>36985.488</t>
+          <t>36985487534.7532</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>39234.344</t>
+          <t>39234343510.477</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>41323.404</t>
+          <t>41323404467.1697</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>44182.958</t>
+          <t>44182957938.851</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>46641.325</t>
+          <t>46641325311.4693</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>43713.681</t>
+          <t>43713680897.2701</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>44470.62</t>
+          <t>44470619925.6281</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>48393.475</t>
+          <t>48393475362.6189</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>48072.498</t>
+          <t>48072498484.4167</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>50685.795</t>
+          <t>50685794643.9838</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>420385.897</t>
+          <t>420385897422.539</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>398133.425</t>
+          <t>398133425167.822</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>428233.725</t>
+          <t>428233725107.012</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>429087.907</t>
+          <t>429087906671.338</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>423530.803</t>
+          <t>423530802773.818</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>435415.42</t>
+          <t>435415420447.596</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>458212.02</t>
+          <t>458212020081.599</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>447714.081</t>
+          <t>447714081085.054</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>490987.886</t>
+          <t>490987886139.768</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>520747.278</t>
+          <t>520747278415.095</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>539454.826</t>
+          <t>539454826270.348</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>544967.401</t>
+          <t>544967401358.161</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>520247.784</t>
+          <t>520247784242.295</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>512318.062</t>
+          <t>512318062279.653</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>540331.643</t>
+          <t>540331643013.75</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2564.961</t>
+          <t>2564960598.84275</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2765.999</t>
+          <t>2765999225.93859</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2562.248</t>
+          <t>2562247561.56878</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2648.308</t>
+          <t>2648307825.29726</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2819.835</t>
+          <t>2819835218.62985</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2985.345</t>
+          <t>2985345085.33351</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3418.575</t>
+          <t>3418575484.79325</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3692.284</t>
+          <t>3692284193.40849</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3498.307</t>
+          <t>3498306962.86072</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3463.682</t>
+          <t>3463682059.36992</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3976.622</t>
+          <t>3976622317.16322</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4151.332</t>
+          <t>4151332138.97484</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>4746.328</t>
+          <t>4746327823.60421</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>4894.88</t>
+          <t>4894879611.64096</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4969.482</t>
+          <t>4969481581.34418</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>31832.62</t>
+          <t>31832620361.4917</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>32417.516</t>
+          <t>32417515580.2283</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>30054.18</t>
+          <t>30054180210.2987</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31058.26</t>
+          <t>31058259897.8744</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>32575.223</t>
+          <t>32575222655.904</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>33608.857</t>
+          <t>33608856561.9837</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>35655.107</t>
+          <t>35655107015.2263</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>37974.542</t>
+          <t>37974541834.1766</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>42871.273</t>
+          <t>42871273042.2151</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>46209.714</t>
+          <t>46209714164.7541</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>47309.84</t>
+          <t>47309840498.8342</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>49537.735</t>
+          <t>49537734660.0265</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>48407.418</t>
+          <t>48407418024.2854</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>46890.862</t>
+          <t>46890862080.2975</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>42144.312</t>
+          <t>42144312417.667</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>157242.594</t>
+          <t>157242594157.723</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>144063.479</t>
+          <t>144063478831.121</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>131512.9</t>
+          <t>131512900295.288</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>127875.975</t>
+          <t>127875974853.143</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>135502.753</t>
+          <t>135502753433.811</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>144432.419</t>
+          <t>144432419446.196</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>143535.48</t>
+          <t>143535479902.654</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>137423.751</t>
+          <t>137423750551.397</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>141230.215</t>
+          <t>141230214978.218</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>149285.336</t>
+          <t>149285336029.248</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>148647.785</t>
+          <t>148647784723.307</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>146452.754</t>
+          <t>146452754338.144</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>136295.829</t>
+          <t>136295829274.194</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>133850.967</t>
+          <t>133850966907.608</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>130875.075</t>
+          <t>130875074667.642</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49479.882</t>
+          <t>49479881518.9271</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48472.564</t>
+          <t>48472563965.8889</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>45398.374</t>
+          <t>45398374096.4522</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>41837.343</t>
+          <t>41837342619.602</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>41835.02</t>
+          <t>41835019737.2204</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>45305.076</t>
+          <t>45305076274.588</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46199.493</t>
+          <t>46199492722.9126</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>47681.299</t>
+          <t>47681298507.4524</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>51334.145</t>
+          <t>51334145490.674</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>55199.37</t>
+          <t>55199370284.6097</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>54886.604</t>
+          <t>54886604183.1071</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>57369.91</t>
+          <t>57369909679.3578</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>55746.306</t>
+          <t>55746306260.2395</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>53073.057</t>
+          <t>53073056635.0457</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>52602.688</t>
+          <t>52602688353.3916</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1545.578</t>
+          <t>1545578460.19967</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1554.288</t>
+          <t>1554287662.54128</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1560.48</t>
+          <t>1560480120.26359</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1875.108</t>
+          <t>1875108353.62609</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1921.061</t>
+          <t>1921060746.49793</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1924.436</t>
+          <t>1924435678.24025</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1806.054</t>
+          <t>1806054255.93329</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1927.487</t>
+          <t>1927487226.77709</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2142.277</t>
+          <t>2142277175.18556</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1962.57</t>
+          <t>1962570071.40436</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2171.254</t>
+          <t>2171253940.47866</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2298.343</t>
+          <t>2298343217.93941</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2377.829</t>
+          <t>2377828928.38884</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2610.198</t>
+          <t>2610198418.68133</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2360.138</t>
+          <t>2360137729.14182</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>584.217</t>
+          <t>584217287.680378</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>526.228</t>
+          <t>526227505.013563</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>463.171</t>
+          <t>463171403.397312</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>484.149</t>
+          <t>484149462.757164</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>541.81</t>
+          <t>541809555.822582</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>586.238</t>
+          <t>586237569.360079</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>574.598</t>
+          <t>574598286.650198</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>638.892</t>
+          <t>638892278.915725</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>682.742</t>
+          <t>682741736.714709</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>743.391</t>
+          <t>743390649.196508</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>799.405</t>
+          <t>799404688.682655</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>804.34</t>
+          <t>804340030.57771</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>762.09</t>
+          <t>762090345.824728</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>902.31</t>
+          <t>902309991.678641</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>806.313</t>
+          <t>806313494.517495</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>943.003</t>
+          <t>943003069.915379</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>979.512</t>
+          <t>979512278.316527</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>956.112</t>
+          <t>956112339.421649</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>984.41</t>
+          <t>984410033.712591</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>998.168</t>
+          <t>998168180.31789</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>873.824</t>
+          <t>873824336.081819</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>834.511</t>
+          <t>834511496.038216</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>814.071</t>
+          <t>814070752.527717</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>868.608</t>
+          <t>868608155.246898</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>901.7</t>
+          <t>901700374.873281</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>986.667</t>
+          <t>986666777.99465</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1117.006</t>
+          <t>1117005941.38927</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1306.402</t>
+          <t>1306402099.87825</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1467.458</t>
+          <t>1467458415.19818</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1141.252</t>
+          <t>1141251517.46757</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21200.904</t>
+          <t>21200904389.4558</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>21078.135</t>
+          <t>21078134725.5264</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21702.584</t>
+          <t>21702584352.1246</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>23641.186</t>
+          <t>23641185935.2962</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>25609.662</t>
+          <t>25609662008.4698</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>27374.636</t>
+          <t>27374635843.0491</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>31115.138</t>
+          <t>31115137776.5372</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>31598.41</t>
+          <t>31598410176.233</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>31912.839</t>
+          <t>31912838510.7992</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>32688.118</t>
+          <t>32688118378.0246</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>33508.798</t>
+          <t>33508797856.9039</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>32864.277</t>
+          <t>32864276816.6835</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>32400.704</t>
+          <t>32400703940.696</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>33701.915</t>
+          <t>33701914986.1262</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>33025.714</t>
+          <t>33025713807.0334</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>180.199</t>
+          <t>180198571.08385</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>195.94</t>
+          <t>195939719.215439</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>158.908</t>
+          <t>158907602.296784</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>174.187</t>
+          <t>174187214.974393</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>202.475</t>
+          <t>202474739.163574</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>219.114</t>
+          <t>219113975.272536</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>252.78</t>
+          <t>252779784.659229</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>273.037</t>
+          <t>273036753.120331</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>307.241</t>
+          <t>307241422.498978</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>245.761</t>
+          <t>245760972.033497</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>253.075</t>
+          <t>253074881.94159</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>249.916</t>
+          <t>249916143.512192</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>276.343</t>
+          <t>276343220.713324</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>314.508</t>
+          <t>314507812.828019</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>277.091</t>
+          <t>277090501.84865</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22178.752</t>
+          <t>22178751719.8234</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21985.107</t>
+          <t>21985107173.9203</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15923.836</t>
+          <t>15923836059.2492</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19768.579</t>
+          <t>19768579268.938</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>21662.56</t>
+          <t>21662559571.2566</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>21107.54</t>
+          <t>21107540190.5547</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>23843.121</t>
+          <t>23843120995.7457</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26893.851</t>
+          <t>26893851364.2482</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>26962.745</t>
+          <t>26962745210.4081</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>26718.151</t>
+          <t>26718150808.9302</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>26003.238</t>
+          <t>26003238335.4179</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>26246.261</t>
+          <t>26246261221.9102</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>27031.605</t>
+          <t>27031605090.798</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>28878.38</t>
+          <t>28878379780.768</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>27946.189</t>
+          <t>27946189368.8835</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>17871.136</t>
+          <t>17871135849.4213</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>18798.201</t>
+          <t>18798201417.9995</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19512.217</t>
+          <t>19512216965.9773</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20064.186</t>
+          <t>20064186355.3467</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18908.856</t>
+          <t>18908855536.3586</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>18493.58</t>
+          <t>18493580435.3753</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>16058.08</t>
+          <t>16058080176.7667</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15299.252</t>
+          <t>15299251920.6358</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>15066.994</t>
+          <t>15066994122.9634</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>14681.148</t>
+          <t>14681148149.7548</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15720.568</t>
+          <t>15720567781.1179</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>16079.975</t>
+          <t>16079974695.5454</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>16839.022</t>
+          <t>16839022086.4845</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>18321.297</t>
+          <t>18321296947.4581</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>16872.353</t>
+          <t>16872353022.5671</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5775.036</t>
+          <t>5775035744.0031</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5924.266</t>
+          <t>5924265734.76012</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5004.497</t>
+          <t>5004496758.14016</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5719.683</t>
+          <t>5719683293.81049</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5917.976</t>
+          <t>5917976298.13861</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6274.46</t>
+          <t>6274459679.17153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6651.359</t>
+          <t>6651359051.15459</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6703.481</t>
+          <t>6703480760.10726</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6916.171</t>
+          <t>6916171175.17288</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>7178.028</t>
+          <t>7178027945.40108</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>7186.182</t>
+          <t>7186181749.62509</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6983.701</t>
+          <t>6983700554.72644</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>7108.106</t>
+          <t>7108106418.26752</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>7509.057</t>
+          <t>7509056699.02104</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>6266.77</t>
+          <t>6266770163.70035</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5914.936</t>
+          <t>5914935649.40073</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5915.224</t>
+          <t>5915224247.64478</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4727.921</t>
+          <t>4727920542.39135</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5722.542</t>
+          <t>5722542488.01839</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6337.967</t>
+          <t>6337967365.2759</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7373.001</t>
+          <t>7373001063.97284</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7907.847</t>
+          <t>7907846711.97413</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6720.22</t>
+          <t>6720220317.46321</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6823.255</t>
+          <t>6823255081.74369</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>6627.638</t>
+          <t>6627638014.73443</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7427.869</t>
+          <t>7427869014.14718</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7469.464</t>
+          <t>7469463647.13866</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>8108.708</t>
+          <t>8108708001.4855</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>8897.465</t>
+          <t>8897465216.66149</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>7988.666</t>
+          <t>7988666235.98208</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>133981.807</t>
+          <t>133981806556.376</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>140238.235</t>
+          <t>140238234998.053</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>127684.56</t>
+          <t>127684560161.105</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>116044.354</t>
+          <t>116044354085.658</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>109495.238</t>
+          <t>109495237984.026</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>123087.836</t>
+          <t>123087836223.074</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>120957.815</t>
+          <t>120957814878.981</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>124984.62</t>
+          <t>124984619872.013</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>135327.581</t>
+          <t>135327581076.78</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>142898.567</t>
+          <t>142898567337.695</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>149486.403</t>
+          <t>149486403378.706</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>148448.224</t>
+          <t>148448223943.995</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>162846.286</t>
+          <t>162846286088.839</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>174450.91</t>
+          <t>174450909900.365</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>173456.98</t>
+          <t>173456979722.551</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1608.224</t>
+          <t>1608224174.7094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1713.113</t>
+          <t>1713112945.01253</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1650.69</t>
+          <t>1650690360.41927</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1624.462</t>
+          <t>1624462440.68883</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1488.556</t>
+          <t>1488555583.97504</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>1517.37</t>
+          <t>1517369860.70355</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1547.82</t>
+          <t>1547820414.38602</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1501.87</t>
+          <t>1501869994.82714</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1686.746</t>
+          <t>1686745912.17149</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1998.825</t>
+          <t>1998824626.5592</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2066.718</t>
+          <t>2066717606.45779</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2209.934</t>
+          <t>2209934469.25613</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2675.812</t>
+          <t>2675812426.70286</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2662.262</t>
+          <t>2662261954.01187</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3084.896</t>
+          <t>3084896159.13777</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1789.912</t>
+          <t>1789911670.67225</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1724.645</t>
+          <t>1724644974.19368</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1507.538</t>
+          <t>1507537625.08461</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1582.07</t>
+          <t>1582070102.65685</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1625.368</t>
+          <t>1625367829.1171</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1669.762</t>
+          <t>1669762218.61143</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1727.927</t>
+          <t>1727927270.07706</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1791.625</t>
+          <t>1791625487.30206</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2030.121</t>
+          <t>2030120894.87491</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1993.431</t>
+          <t>1993431319.69058</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1934.689</t>
+          <t>1934688798.47672</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1966.974</t>
+          <t>1966973722.97779</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2000.22</t>
+          <t>2000220228.00933</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2739.73</t>
+          <t>2739730025.24432</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2688.978</t>
+          <t>2688977900.7358</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9515.748</t>
+          <t>9515747983.38527</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9896.54</t>
+          <t>9896540345.55393</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>8636.841</t>
+          <t>8636841378.34141</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9471.131</t>
+          <t>9471130729.53754</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9845.335</t>
+          <t>9845334534.94053</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>11117.745</t>
+          <t>11117744799.753</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11424.323</t>
+          <t>11424323403.4135</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11906.723</t>
+          <t>11906722610.2897</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>12819.618</t>
+          <t>12819618174.2714</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>13361.829</t>
+          <t>13361828762.693</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>13753.319</t>
+          <t>13753318695.5332</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>13915.92</t>
+          <t>13915920176.7677</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>14909.593</t>
+          <t>14909592768.8742</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>13722.015</t>
+          <t>13722014662.8459</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>11912.724</t>
+          <t>11912724478.9477</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>10871.822</t>
+          <t>10871821569.3246</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>12649.293</t>
+          <t>12649292585.7376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13536.785</t>
+          <t>13536784516.6845</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>13427.769</t>
+          <t>13427768545.6196</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>13741.414</t>
+          <t>13741413662.713</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>12809.007</t>
+          <t>12809006627.7098</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11414.018</t>
+          <t>11414018142.3802</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>10559.419</t>
+          <t>10559418930.4441</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>11611.224</t>
+          <t>11611224115.7988</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>12557.425</t>
+          <t>12557425351.2796</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>12990.999</t>
+          <t>12990998667.146</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>12780.496</t>
+          <t>12780495812.217</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>13205.656</t>
+          <t>13205655689.2183</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>24916.308</t>
+          <t>24916308159.978</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>21936.863</t>
+          <t>21936863473.7041</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>17530.741</t>
+          <t>17530740735.8185</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>18831.43</t>
+          <t>18831430227.5741</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>17518.397</t>
+          <t>17518397186.2553</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>17250.912</t>
+          <t>17250911690.4574</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>17655.083</t>
+          <t>17655083094.2351</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>19212.684</t>
+          <t>19212683936.5402</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>18988.861</t>
+          <t>18988860615.6505</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>18992.668</t>
+          <t>18992668149.4602</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19498.408</t>
+          <t>19498407770.8072</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>20039.098</t>
+          <t>20039098390.3021</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>20541.741</t>
+          <t>20541741066.9844</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>20607.202</t>
+          <t>20607201643.4605</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>19415.064</t>
+          <t>19415063510.1775</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>19686.422</t>
+          <t>19686422309.4731</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>17843.589</t>
+          <t>17843589490.2924</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>290406.386</t>
+          <t>290406385543.561</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>293950.144</t>
+          <t>293950143661.481</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>301287.615</t>
+          <t>301287615183.409</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>326187.496</t>
+          <t>326187496097.005</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>342755.749</t>
+          <t>342755749115.23</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>384745.14</t>
+          <t>384745139633.272</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>400497.842</t>
+          <t>400497841957.687</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>408819.562</t>
+          <t>408819562454.388</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>419320.529</t>
+          <t>419320529434.201</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>433843.884</t>
+          <t>433843883936.475</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>441648.055</t>
+          <t>441648054953.128</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>444016.965</t>
+          <t>444016965450.416</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>426908.083</t>
+          <t>426908083088.703</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>410499.95</t>
+          <t>410499950071.402</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>391462.67</t>
+          <t>391462669977.231</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1412710.619</t>
+          <t>1412710619221.51</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1425143.913</t>
+          <t>1425143912987.41</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1498134.134</t>
+          <t>1498134133934.28</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1524721.598</t>
+          <t>1524721597660.27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1578145.664</t>
+          <t>1578145664285.07</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1705732.089</t>
+          <t>1705732088568.04</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1777652.025</t>
+          <t>1777652024725.55</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1812795.584</t>
+          <t>1812795583981.11</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1862340.013</t>
+          <t>1862340013147.2</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>1895745.656</t>
+          <t>1895745656102.62</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>1975794.288</t>
+          <t>1975794288355</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2054831.762</t>
+          <t>2054831761791.48</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2013243.836</t>
+          <t>2013243835846.95</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2100958.935</t>
+          <t>2100958934527.76</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2136023.513</t>
+          <t>2136023513280.6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3763194.167</t>
+          <t>3763194167400.86</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>3749544.115</t>
+          <t>3749544115210.12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3795961.601</t>
+          <t>3795961601114.17</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>3853920.145</t>
+          <t>3853920145352.32</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>3933919.494</t>
+          <t>3933919494171.28</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4149537.481</t>
+          <t>4149537480855.06</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4281703.68</t>
+          <t>4281703679803.06</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4340942.504</t>
+          <t>4340942504211.43</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4510801.759</t>
+          <t>4510801758824.33</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4642986.001</t>
+          <t>4642986000831.68</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>4763031.699</t>
+          <t>4763031699463.83</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4867400.419</t>
+          <t>4867400419142.14</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>4761877.896</t>
+          <t>4761877896386.33</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>4881306.754</t>
+          <t>4881306754480.28</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>4886466.877</t>
+          <t>4886466876530.36</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
